--- a/ยอดเสีย5เปอร์เซ็น UFRUV.xlsx
+++ b/ยอดเสีย5เปอร์เซ็น UFRUV.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>ยูส</t>
   </si>
@@ -22,19 +22,19 @@
     <t>ufruv010210539</t>
   </si>
   <si>
+    <t>105.51500000000001</t>
+  </si>
+  <si>
+    <t>ufruv010210655</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>ufruv010210655</t>
-  </si>
-  <si>
-    <t>169.51</t>
-  </si>
-  <si>
     <t>ufruv010210798</t>
   </si>
   <si>
-    <t>361.9205</t>
+    <t>118.081</t>
   </si>
   <si>
     <t>ufruv010210856</t>
@@ -43,45 +43,24 @@
     <t>ufruv01023517</t>
   </si>
   <si>
-    <t>ufruv01029080</t>
-  </si>
-  <si>
-    <t>ufruv01039024</t>
+    <t>687.5</t>
   </si>
   <si>
     <t>ufruv01055614</t>
   </si>
   <si>
-    <t>483.54750000000007</t>
-  </si>
-  <si>
-    <t>ufruv010610864</t>
+    <t>ufruv010612412</t>
   </si>
   <si>
     <t>ufruv01065677</t>
   </si>
   <si>
-    <t>ufruv010710635</t>
-  </si>
-  <si>
     <t>ufruv010711474</t>
   </si>
   <si>
     <t>ufruv010711499</t>
   </si>
   <si>
-    <t>ufruv010711501</t>
-  </si>
-  <si>
-    <t>ufruv010711502</t>
-  </si>
-  <si>
-    <t>ufruv010711503</t>
-  </si>
-  <si>
-    <t>ufruv010711504</t>
-  </si>
-  <si>
     <t>ufruv010711505</t>
   </si>
   <si>
@@ -91,103 +70,79 @@
     <t>ufruv010711509</t>
   </si>
   <si>
-    <t>ufruv010711510</t>
-  </si>
-  <si>
     <t>ufruv010711568</t>
   </si>
   <si>
-    <t>ufruv010711592</t>
-  </si>
-  <si>
     <t>ufruv010711624</t>
   </si>
   <si>
-    <t>ufruv010711897</t>
-  </si>
-  <si>
     <t>ufruv010712080</t>
   </si>
   <si>
+    <t>ufruv010712283</t>
+  </si>
+  <si>
+    <t>ufruv010712458</t>
+  </si>
+  <si>
+    <t>ufruv010712720</t>
+  </si>
+  <si>
     <t>ufruv01075852</t>
   </si>
   <si>
-    <t>ufruv01078473</t>
-  </si>
-  <si>
-    <t>ufruv020410176</t>
-  </si>
-  <si>
-    <t>ufruv02048600</t>
-  </si>
-  <si>
-    <t>ufruv030210522</t>
-  </si>
-  <si>
-    <t>ufruv040110188</t>
-  </si>
-  <si>
-    <t>ufruv040110189</t>
-  </si>
-  <si>
-    <t>ufruv040110223</t>
-  </si>
-  <si>
-    <t>ufruv040110405</t>
-  </si>
-  <si>
-    <t>ufruv040110587</t>
-  </si>
-  <si>
-    <t>ufruv04019189</t>
-  </si>
-  <si>
-    <t>ufruv04028756</t>
-  </si>
-  <si>
-    <t>ufruv050110686</t>
-  </si>
-  <si>
-    <t>479.95150000000007</t>
-  </si>
-  <si>
-    <t>ufruv050110687</t>
-  </si>
-  <si>
-    <t>ufruv050110692</t>
-  </si>
-  <si>
-    <t>ufruv050110941</t>
-  </si>
-  <si>
-    <t>ufruv050110942</t>
-  </si>
-  <si>
-    <t>ufruv050111027</t>
-  </si>
-  <si>
-    <t>ufruv050111352</t>
-  </si>
-  <si>
-    <t>ufruv050210724</t>
-  </si>
-  <si>
-    <t>ufruv050310895</t>
-  </si>
-  <si>
-    <t>ufruv050310935</t>
-  </si>
-  <si>
-    <t>ufruv050310955</t>
-  </si>
-  <si>
-    <t>111.97950000000002</t>
-  </si>
-  <si>
-    <t>ufruv050310963</t>
-  </si>
-  <si>
-    <t>ufruv050410968</t>
+    <t>ufruv010312534</t>
+  </si>
+  <si>
+    <t>ufruv040113594</t>
+  </si>
+  <si>
+    <t>ufruv040113595</t>
+  </si>
+  <si>
+    <t>ufruv040113624</t>
+  </si>
+  <si>
+    <t>ufruv040113627</t>
+  </si>
+  <si>
+    <t>ufruv040113629</t>
+  </si>
+  <si>
+    <t>ufruv040113635</t>
+  </si>
+  <si>
+    <t>ufruv040113637</t>
+  </si>
+  <si>
+    <t>ufruv040113642</t>
+  </si>
+  <si>
+    <t>ufruv040113648</t>
+  </si>
+  <si>
+    <t>ufruv040113661</t>
+  </si>
+  <si>
+    <t>ufruv040113662</t>
+  </si>
+  <si>
+    <t>ufruv040113743</t>
+  </si>
+  <si>
+    <t>ufruv040113753</t>
+  </si>
+  <si>
+    <t>ufruv040113779</t>
+  </si>
+  <si>
+    <t>ufruv040113792</t>
+  </si>
+  <si>
+    <t>ufruv040113934</t>
+  </si>
+  <si>
+    <t>ufruv040114044</t>
   </si>
 </sst>
 </file>
@@ -227,7 +182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -267,7 +222,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -275,31 +230,31 @@
         <v>9</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -307,7 +262,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -315,7 +270,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -323,7 +278,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -331,7 +286,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -339,7 +294,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -347,7 +302,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -355,7 +310,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -363,7 +318,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -371,7 +326,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -379,7 +334,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -387,7 +342,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -395,7 +350,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -403,7 +358,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -411,7 +366,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -419,7 +374,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -427,7 +382,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -435,7 +390,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -443,7 +398,7 @@
         <v>31</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -451,7 +406,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -459,7 +414,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -467,7 +422,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -475,7 +430,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -483,7 +438,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -491,7 +446,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -499,7 +454,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -507,7 +462,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -515,7 +470,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -523,7 +478,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -531,7 +486,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -539,111 +494,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/ยอดเสีย5เปอร์เซ็น UFRUV.xlsx
+++ b/ยอดเสีย5เปอร์เซ็น UFRUV.xlsx
@@ -11,12 +11,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ยูส</t>
   </si>
   <si>
     <t>ยอด</t>
+  </si>
+  <si>
+    <t>ufruv010210655</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ufruv01023517</t>
+  </si>
+  <si>
+    <t>ufruv010319435</t>
+  </si>
+  <si>
+    <t>ufruv01038594</t>
+  </si>
+  <si>
+    <t>ufruv01065677</t>
+  </si>
+  <si>
+    <t>ufruv010711474</t>
+  </si>
+  <si>
+    <t>ufruv010711624</t>
+  </si>
+  <si>
+    <t>ufruv010712720</t>
+  </si>
+  <si>
+    <t>ufruv011018652</t>
+  </si>
+  <si>
+    <t>ufruv011018662</t>
+  </si>
+  <si>
+    <t>ufruv011018664</t>
+  </si>
+  <si>
+    <t>ufruv011019173</t>
+  </si>
+  <si>
+    <t>ufruv040114045</t>
+  </si>
+  <si>
+    <t>ufruv050110687</t>
+  </si>
+  <si>
+    <t>ufruv050111352</t>
+  </si>
+  <si>
+    <t>ufruv050115411</t>
+  </si>
+  <si>
+    <t>ufruv050310935</t>
+  </si>
+  <si>
+    <t>ufruv050310955</t>
+  </si>
+  <si>
+    <t>ufruv050310963</t>
   </si>
 </sst>
 </file>
@@ -56,7 +116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -67,6 +127,158 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
